--- a/docs/quality/Coreon-EDU_Product-Inventory.xlsx
+++ b/docs/quality/Coreon-EDU_Product-Inventory.xlsx
@@ -17,6 +17,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bahreïn Go-Live" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tests &amp; CI" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dettes &amp; Décisions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FAT 2026-07-26" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Norme d'acceptation v1" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Modules (cœur)'!$A$4:$G$4</definedName>
@@ -28,6 +30,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Bahreïn Go-Live'!$A$4:$E$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Tests &amp; CI'!$A$4:$D$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Dettes &amp; Décisions'!$A$4:$D$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'FAT 2026-07-26'!$A$4:$D$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Norme d''acceptation v1'!$A$4:$F$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1018,6 +1022,1224 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="86" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>FAT EXPLORATOIRE — 5 rapports QA (méthode « rejeter la livraison »)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Chaque ingénieur QA a piloté un vrai navigateur, école configurée BAHREÏN, en EN et AR. Les 5 ont voté REJET.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Sévérité</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Domaine</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Constat</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>REJET</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Vérité UI</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>« Suspendre l'école » ne coupait AUCUN accès (badge décoratif)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>REJET</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Vérité UI</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Le provisionnement affichait un mot de passe sans CRÉER le compte</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>REJET</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Vérité UI</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Registre visiteurs : affichait « CPR », enregistrait « CIN »</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>REJET</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Vérité UI</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier : en-têtes Lun–Dim sur une grille commençant dimanche</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>REJET</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Vérité UI</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>« Joignable : Oui » codé en dur, sans aucune sonde</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>REJET</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Argent</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>/app/finance CRASHAIT pour toute l'école dès la 1re inscription réelle</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>REJET</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Argent</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Annuler une facture PAYÉE faisait disparaître l'encaissé des états</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>REJET</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Argent</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>money() : format français en anglais (12,345 lu « douze mille ») + décimales mixtes</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>REJET</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Argent</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Arrondi au dinar entier : chaque remise % volait ~234 fils</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>REJET</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Légal</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Inscription : « loi 2004-63 » (tunisienne) sous une case PDPL bahreïnie</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>REJET</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Légal</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Certificats et documents signés « (INPDP) » — autorité tunisienne</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>REJET</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Données</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Groupe sanguin « O+ » présélectionné ET ENREGISTRÉ (donnée médicale inventée)</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>REJET</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Fonctionnel</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Une CRÈCHE ne pouvait inscrire personne (niveaux 1ère–6ème seulement)</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>REJET</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Fonctionnel</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Formulaire élève : nom de 500 car., naissance 1900, tél « abc### » acceptés</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>REJET</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>RTL</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Arabe : téléphones affichés À L'ENVERS (« 111 111 20 216+ »), chiffres brouillés</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>REJET</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Robustesse</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Hors-ligne : chunk paresseux en échec = ÉCRAN BLANC muet</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>REJET</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Démo</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>8 élèves homonymes par classe (« Chaima Karoui » ×8) — graine non crédible</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>MAJEUR</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Fonctionnel</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Appel : ré-enregistrer re-notifiait TOUS les parents</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>MAJEUR</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Mes paiements : AUCUN montant, aucune devise</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>MAJEUR</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Confirmations</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Accident→parent, journal→parent, vider un jour de cantine : sans confirmation</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>MAJEUR</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Rôles</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>RH et Comptabilité privés de Demandes / Espaces / Pointage (CR-019 incomplet)</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>MAJEUR</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Rôles</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>RH ne pouvait pas décider un congé ; sécurité/RH/compta absents de l'appel</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>MAJEUR</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Autorisation</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>requests.js : assign/close SANS contrôle de rôle (garde uniquement à l'écran)</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>MAJEUR</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Honnêteté</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Badge « EN DIRECT » sur une journée SIMULÉE montré au parent</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>MAJEUR</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Admissions</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Refuser un enfant : 1 clic, sans confirmation ni motif (le recrutement, lui, exige un motif)</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>MAJEUR</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>i18n</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Toasts français derrière des boutons anglais (appel, moment, validation, envoi)</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-26 (FAT QA v1.4/v1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Argent</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Deux modèles d'argent (factures vs grille mensuelle) peuvent se contredire</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT — D5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Argent</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Location et activités : encaissement sans reçu numéroté, hors comptabilité</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT — D5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Sécurité</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Journal d'audit inexistant (qui a lu un dossier médical) — exigence PDPL</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT — D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>i18n</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>~310 clés encore non traduites (EN 62 %, AR 63 %)</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT — D4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Exploitation</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Hébergement serveur inexistant : données dans le navigateur, mots de passe en clair</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT — D9</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Exploitation</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Aucune supervision (Sentry/sonde) ni restauration de sauvegarde répétée</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT — D9</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Pays</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>TVA 10 % / facture NBR · GOSI-EOSB dans la paie · reporting MOE</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT — D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Tuiles du tableau de bord n'ouvrent pas toutes le détail ; pas d'édition/archivage élève</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT — D8</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:D4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>NORME D'ACCEPTATION PRODUIT v1 (2026-07-26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Ce que « acceptable pour une école qui paie » veut dire — critère, mesure exécutable, état. Détail : docs/quality/ACCEPTANCE-STANDARD-v1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Domaine</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Critère</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Comment on le mesure</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>État</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Ce qui manque</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Intégrité fonctionnelle</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Aucun écran ne casse ; actions irréversibles confirmées ; aucune donnée inventée</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>core: npm test · e2e: npm run all · node e2e/fat.mjs</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>CONFORME</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Vérité de l'interface</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Ce que l'écran affirme est VRAI (bouton, identifiant, état mesuré)</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Revue FAT exploratoire par rôle</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>CONFORME</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Conformité pays</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Semaine, devise, pièce, loi, urgences, fériés : du pack, jamais en dur</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>node e2e/diag.feries-pays.mjs · node e2e/fat.mjs</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>PARTIEL</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>TVA/NBR · GOSI-EOSB · reporting MOE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Langue FR/EN/AR</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Aucune phrase d'une autre langue à l'écran</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>python3 docs/quality/i18n-audit.py</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>PARTIEL</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>EN 62 % / AR 63 % → seuil client 95 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Intégrité de l'argent</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Rien ne disparaît ; arrondi au fils ; format par langue ; écritures confirmées</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Tests cœur compta/paie + revue FAT argent</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>PARTIEL</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Unifier les 2 modèles · reçus location/activités</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Sécurité &amp; données</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Pas de secret, pas d'élévation, accès par rôle, consentement pays, audit</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>securite.yml (CodeQL+secrets) · server tests</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>PARTIEL</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Journal d'audit · sortir du mode démo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Données du client</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Entrée sans ressaisie, sortie libre</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>node e2e/diag.import.mjs · export OneRoster</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>CONFORME</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>(ZIP d'export : confort)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>UX &amp; accessibilité</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Pas d'écran blanc, états complets, RTL, clavier, contraste</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>e2e parcours.qualite (axe) · parcours.uiux (25 pages)</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>CONFORME</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>D9</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Exploitation</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>3 environnements, tests bloquants, retour arrière, sauvegardes, supervision</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>deploy.yml + envs.yml</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>PARTIEL</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>HÉBERGEMENT SERVEUR · supervision · restauration testée</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Preuve &amp; documentation</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Tout ce qui est affirmé est mesurable et daté</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Ce classeur + ACCEPTANCE-STANDARD-v1.md</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>CONFORME</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>PRONONCÉ v1.5.0</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>PILOTE ACCOMPAGNÉ : oui — LIVRAISON AUTONOME : pas encore</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>PILOTE</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>3 portes : D9 hébergement → D4 langue 95 % → D5/D3 argent &amp; conformité</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:F4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/quality/Coreon-EDU_Product-Inventory.xlsx
+++ b/docs/quality/Coreon-EDU_Product-Inventory.xlsx
@@ -2246,7 +2246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2557,302 +2557,302 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>audit.js</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>CR-039 · journal d’audit : qui a lu / modifié un dossier sensible</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>9 tests cœur (falsification, rotation comptée, purge non destructrice, injection CSV) + e2e/parcours.audit.mjs</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>AJOUTÉ 2026-08-01. Clé de stockage séparée du blob (sinon mergeWrite le rendrait réécrivable) ; chaîne d’empreintes tamper-ÉVIDENTE, pas tamper-proof ; aucun chemin de suppression. RESTE : immuabilité réelle = table serveur en AJOUT SEUL (D9)</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>LIVRÉ 2026-08-01 (CR-039)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
           <t>admissions.js</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Pipeline candidature → inscription</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>3 tests</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>advance() TypeError sur étape inconnue ; DOCS tunisiens non pack ; CAPACITY dupliqué ; pas de promotion de liste d’attente</t>
         </is>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E13" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>auth.js</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Session 8 h par la couture stockage</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>1 test</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Comparaison de mot de passe EN CLAIR (mode démo) ; loginAs = primitive d’usurpation exportée ; throw si user sans email ; TTL non glissant</t>
         </is>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E14" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>OUVERT (mode démo par design — voir hébergement)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>behavior.js</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Observations positives d’abord, climat de classe</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>4 tests</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>Bug Date → climat VIDE sur données réelles ; parent lié par childIds seul jamais notifié ; entriesFor exporté non filtré</t>
         </is>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>OUVERT (bug Date = chantier now())</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>budget.js</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Livre de dépenses + rapports réels</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>1 test</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Salaires sous-évalués si prime (bug setBonus — corrigé) ; 24 relectures db()/graphique ; pas de prévisionnel</t>
         </is>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E16" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>CORRIGÉ 2026-07-25 (6dcc445) (via hr.js)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>canteen.js</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Menu semaine + ALERTE ALLERGIE calculée</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>3 tests</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Correspondance FRANÇAIS uniquement — « Peanut allergy » / arabe = AUCUNE alerte (sécurité enfant !) ; faux positif « Peau sensible »→gluten ; jours lun–ven (pas de dimanche BH) ; ignore childcare.healthOf</t>
         </is>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="E17" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>charts.js</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Jetons graphiques Recharts</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Objets Recharts dans le cœur « neutre » ; règle 7e série non implémentée</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E18" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>childcare.js</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Dossier enfant : vaccins, personnes autorisées, jalons</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>règle n°1</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>VACCINS = calendrier TUNISIEN (exposition réglementaire BH) ; monthsOld ±30 j ; remise d’enfant sans vérif d’identité ni doublon</t>
         </is>
       </c>
-      <c r="E18" s="7" t="n">
+      <c r="E19" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>clock.js</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Horloge, jour d’école, rentrée, mode démo</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>3 tests</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>now() renvoie une Date (racine du bug NaN post-rechargement, 8+ modules) ; week-end dim/sam + semaine lun–ven EN DUR (BH = dim–jeu !) ; 08:00–15:00 fixe ; rentrée 15 sept fixe ; aucun fuseau</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>OUVERT — LE chantier calendrier</t>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>currency.js</t>
+          <t>clock.js</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Devise active + money()</t>
+          <t>Horloge, jour d’école, rentrée, mode démo</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>AUCUN direct</t>
+          <t>3 tests</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>fr-FR en dur ; BHD sans millièmes (12,5 lu douze mille cinq cents)</t>
+          <t>now() renvoie une Date (racine du bug NaN post-rechargement, 8+ modules) ; week-end dim/sam + semaine lun–ven EN DUR (BH = dim–jeu !) ; 08:00–15:00 fixe ; rentrée 15 sept fixe ; aucun fuseau</t>
         </is>
       </c>
       <c r="E20" s="8" t="n">
@@ -2865,33 +2865,33 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>CORRIGÉ 2026-07-25 (6dcc445) (décimales) ; locale à faire</t>
+          <t>OUVERT — LE chantier calendrier</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>data.js</t>
+          <t>currency.js</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Emploi du temps enseignant + éval (questions/paniers)</t>
+          <t>Devise active + money()</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>AUCUN</t>
+          <t>AUCUN direct</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>SCHEDULE DE DÉMO EN DUR servi à TOUT enseignant ; teacherTimetable généré par hachage ≠ grille Direction ; jours/heures fixes</t>
+          <t>fr-FR en dur ; BHD sans millièmes (12,5 lu douze mille cinq cents)</t>
         </is>
       </c>
       <c r="E21" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
@@ -2900,274 +2900,274 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>OUVERT</t>
+          <t>CORRIGÉ 2026-07-25 (6dcc445) (décimales) ; locale à faire</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
+          <t>data.js</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Emploi du temps enseignant + éval (questions/paniers)</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>AUCUN</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>SCHEDULE DE DÉMO EN DUR servi à TOUT enseignant ; teacherTimetable généré par hachage ≠ grille Direction ; jours/heures fixes</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
           <t>db.js</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Persistance : graine, migration v24, refs, liens parent↔enfant</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>8 tests</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>db() = parse COMPLET à chaque appel (chemins chauds par ligne !) ; install neuve = AUTO-GRAINE école démo + mots de passe publiés (Setup ne purge pas) ; quota 5 Mo ; uid Math.random</t>
         </is>
       </c>
-      <c r="E22" s="8" t="n">
+      <c r="E23" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>OUVERT — bloqueur d’expédition</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>documents.js</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Certificats numérotés, registre append-only</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>1 test</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>Numérotation length+1 (doublons après restauration) ; AUCUN gabarit rendu (le document physique n’existe pas) ; types tunisiens</t>
         </is>
       </c>
-      <c r="E23" s="7" t="n">
+      <c r="E24" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>enrolment.js</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Schéma multi-étapes pré-inscription</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>8 tests (le mieux couvert)</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>Placeholders tunisiens ; consentement générique au lieu du texte légal du pack ; pas de contrôle âge/niveau ; pas de détection de doublon</t>
         </is>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>facilities.js</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Location d’installations</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>règle n°8</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>priceFor renvoie 0|objet → réservation à prix undefined → revenus NaN ; bookRecurring bug UTC ; encaissement HORS comptabilité</t>
         </is>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E26" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>features.js</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Modules on/off + surcharges école</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>1 test</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>Surcharges lues à l’import (RN cassé) ; setModuleOverrides ne persiste pas ; pas de graphe de dépendances</t>
         </is>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E27" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>fetes.js</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Fériés par pays + hégirien</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>4 tests</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>BH Fitr 2 j au lieu de 3 (corrigé) ; tables s’arrêtent à 2027 ; férié non relié présence/paie</t>
         </is>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="E28" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>CORRIGÉ 2026-07-25 (6dcc445) (Fitr 3 j)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>gallery.js</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Moments photo, règle de vie privée dans le cœur</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>2 tests</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>consentOnly ignoré (corrigé) ; removeMoment suppression dure sans contrôle ; bug Date tri ; base64 dans le quota</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>CORRIGÉ 2026-07-25 (6dcc445) (consentOnly)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>hr.js</t>
+          <t>gallery.js</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Contrats multi-composants, congés, paie maker-checker</t>
+          <t>Moments photo, règle de vie privée dans le cœur</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>4 tests</t>
+          <t>2 tests</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>setBonus total périmé (corrigé) ; congés décomptent week-ends/fériés ; PAS de GOSI/EOSB (obligatoire BH) ; 2 modèles de congés parallèles</t>
+          <t>consentOnly ignoré (corrigé) ; removeMoment suppression dure sans contrôle ; bug Date tri ; base64 dans le quota</t>
         </is>
       </c>
       <c r="E29" s="8" t="n">
@@ -3180,29 +3180,29 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>CORRIGÉ 2026-07-25 (6dcc445) (setBonus) ; GOSI/EOSB = CR-028</t>
+          <t>CORRIGÉ 2026-07-25 (6dcc445) (consentOnly)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>i18n.js</t>
+          <t>hr.js</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>FR→AR, direction, dates</t>
+          <t>Contrats multi-composants, congés, paie maker-checker</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>3 tests</t>
+          <t>4 tests</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>PAS d’anglais (BH = ar + en !) ; ~38 pages à 0 % ; t() sans interpolation/pluriels ; ar-TN pour BH</t>
+          <t>setBonus total périmé (corrigé) ; congés décomptent week-ends/fériés ; PAS de GOSI/EOSB (obligatoire BH) ; 2 modèles de congés parallèles</t>
         </is>
       </c>
       <c r="E30" s="8" t="n">
@@ -3215,453 +3215,453 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
+          <t>CORRIGÉ 2026-07-25 (6dcc445) (setBonus) ; GOSI/EOSB = CR-028</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>i18n.js</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>FR→AR, direction, dates</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>3 tests</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>PAS d’anglais (BH = ar + en !) ; ~38 pages à 0 % ; t() sans interpolation/pluriels ; ar-TN pour BH</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
           <t>OUVERT — chantier majeur</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>insights.js</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Intelligence : climat, présence, recouvrement</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>4 tests</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>Climat vide sur données réelles (bug Date) ; recouvrement lit l’ANCIEN modèle payments (démo pour toujours)</t>
         </is>
       </c>
-      <c r="E31" s="7" t="n">
+      <c r="E32" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>inventory.js</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>Stock léger avec mouvements</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>1 test</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>Journal tronqué à 30 mouvements (promesse de traçabilité rompue) ; pas d’unité/coût/péremption</t>
         </is>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E33" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>journal.js</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Journal petite enfance (LE différenciateur)</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>AUCUN TEST</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>napMinutes NaN (bug Date) ; 2 parses par tape ; 2 tablettes s’écrasent ; pas de biberon/médicament/température ; pas de dé-envoi</t>
         </is>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="E34" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>levels.js</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>Colonne vertébrale niveaux/cycles/modules</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>indirect i18n</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>École non configurée = PRIMAIRE par défaut → PERD la petite enfance (le différenciateur) ; libellés FR sans pack (KG1/Grade 1)</t>
         </is>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>livestatus.js</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>« Où est mon enfant » simulé</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>Été = juil–15 sept tunisien ; vendredi BH = affiche LUNDI « en classe » ; récrés en dur ; throw sur emploi du temps vide</t>
         </is>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="E36" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>OUVERT (chantier calendrier)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>locales.js</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Packs pays BH/QA/TN/LY</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>12 tests (le pilier)</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>validId décoratif (accepte « abcde ») ; MANQUENT : week-end, fuseau, horaires, année scolaire, semestres, n° urgence — la racine de tous les bugs calendrier</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>OUVERT — étendre le pack</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
+          <t>locales.js</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Packs pays BH/QA/TN/LY</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>12 tests (le pilier)</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>validId décoratif (accepte « abcde ») ; MANQUENT : week-end, fuseau, horaires, année scolaire, semestres, n° urgence — la racine de tous les bugs calendrier</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>OUVERT — étendre le pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
           <t>mailer.js</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Canal email unique</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>1 test</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>Pas de validation d’adresse ; échecs non persistés ; N envois non attendus par classe ; /api/mail INEXISTANT côté serveur</t>
         </is>
       </c>
-      <c r="E37" s="7" t="n">
+      <c r="E38" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>mark.js / tokens.js / theme.js</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>Marque, jetons, accents par rôle</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>2 sources du logo ; FONT display Sora ≠ police chargée ; 2 hex inventés (hr/accountant) ; mix() sRGB naïf</t>
         </is>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E39" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F39" s="9" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>meteo.js</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Météo Open-Meteo</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>Villes TUNISIENNES seulement — Manama voit la météo de TUNIS ; pas de timeout</t>
         </is>
       </c>
-      <c r="E39" s="7" t="n">
+      <c r="E40" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>nav.js</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>Navigation étagée par rôle</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>2 tests i18n</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>NAV figée au chargement du module ; hr/accountant sans Tableau de bord/Messages/Annonces (corrigé)</t>
         </is>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="E41" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F41" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr">
         <is>
           <t>CORRIGÉ 2026-07-25 (6dcc445)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>notify.js</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>Notifications in-app + email</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>2 tests</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>« École Al-Nour » signait chaque email (corrigé) ; markRead throw sur base neuve ; parents privés des diffusions par rôle en mode serveur ; croissance non bornée</t>
         </is>
       </c>
-      <c r="E41" s="7" t="n">
+      <c r="E42" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>CORRIGÉ 2026-07-25 (6dcc445) (nom école)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>oneroster.js</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>Export OneRoster v1.2 (argument de vente)</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>AUCUN TEST</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>Année 2025-2026 EN DUR ; classes à trait d’union perdent leurs inscriptions ; 200 classes synthétiques ; 1 seul enseignant/classe</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="G42" s="9" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>opsprofile.js</t>
+          <t>oneroster.js</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Fiche technique école</t>
+          <t>Export OneRoster v1.2 (argument de vente)</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>2 tests</t>
+          <t>AUCUN TEST</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Étiquettes live/démo INVERSÉES ; « Joignable : Oui » sans sonde ; 3 hôtes canoniques différents</t>
+          <t>Année 2025-2026 EN DUR ; classes à trait d’union perdent leurs inscriptions ; 200 classes synthétiques ; 1 seul enseignant/classe</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
@@ -3677,22 +3677,22 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>recruit.js</t>
+          <t>opsprofile.js</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Pipeline recrutement</t>
+          <t>Fiche technique école</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>1 test</t>
+          <t>2 tests</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>TypeError sur étape inconnue ; ids hors uid()/refs ; pas d’ACL interne ; PII candidats sans rétention</t>
+          <t>Étiquettes live/démo INVERSÉES ; « Joignable : Oui » sans sonde ; 3 hôtes canoniques différents</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
@@ -3710,35 +3710,35 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>refs.js</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>Référence ERP + uuid + QR</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>9 tests (excellent)</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>nextRef sous blob ACL réduit RÉÉMET la séquence 1 (doublons) ; route /verifier inexistante ; Luhn lettres faible</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>recruit.js</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Pipeline recrutement</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>1 test</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>TypeError sur étape inconnue ; ids hors uid()/refs ; pas d’ACL interne ; PII candidats sans rétention</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
         <is>
           <t>OUVERT</t>
         </is>
@@ -3747,68 +3747,68 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
+          <t>refs.js</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Référence ERP + uuid + QR</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>9 tests (excellent)</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>nextRef sous blob ACL réduit RÉÉMET la séquence 1 (doublons) ; route /verifier inexistante ; Luhn lettres faible</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
           <t>requests.js</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>Circuit demandes : assigner→échéance→clore</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>2 tests</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>AUCUNE autorisation (chacun peut clore la demande d’autrui) ; monthReport mélange mois et aujourd’hui</t>
         </is>
       </c>
-      <c r="E46" s="7" t="n">
+      <c r="E47" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>results.js</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>Scores, mentions, bulletins</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>1 test</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>mentionFor /100 EN DUR vs barème pays (/20 TN) → mentions FAUSSES ; bulletinFor O(jours×classes) et compte d’autres classes</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>OUVERT</t>
         </is>
@@ -3817,267 +3817,267 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
+          <t>results.js</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Scores, mentions, bulletins</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>1 test</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>mentionFor /100 EN DUR vs barème pays (/20 TN) → mentions FAUSSES ; bulletinFor O(jours×classes) et compte d’autres classes</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
           <t>security.js</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>Poste de sécurité : urgences, consignes, rondes</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>AUCUN TEST</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>N° D’URGENCE TUNISIENS EN DUR (BH = 999) aussi dans le texte des consignes ; badge collision &gt;999 ; FR seulement</t>
         </is>
       </c>
-      <c r="E48" s="8" t="n">
+      <c r="E49" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F48" s="8" t="inlineStr">
+      <c r="F49" s="8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>OUVERT — sécurité des personnes</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>social.js</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Espaces &amp; activités, quorum, double approbation</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>2 tests</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>sweep() mute pendant le rendu + parent ne persiste pas (états divergents) ; liste d’attente bloquée par une grande famille ; prix catalogues en DT implicite ; fuseaux</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
+          <t>social.js</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Espaces &amp; activités, quorum, double approbation</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>2 tests</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>sweep() mute pendant le rendu + parent ne persiste pas (états divergents) ; liste d’attente bloquée par une grande famille ; prix catalogues en DT implicite ; fuseaux</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
           <t>storage.js</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>LA couture plateforme (web/RN/serveur)</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>1 test ciblé (excellent)</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>Plafond 5 Mo = LA limite produit (500 élèves ≈ 4,5 Mo) ; impl capturée au chargement</t>
         </is>
       </c>
-      <c r="E50" s="7" t="n">
+      <c r="E51" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G50" s="7" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>OUVERT (= hébergement backend)</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>subjects.js</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>Matière → icône/teinte</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t>Regex FR/latin : « English »/arabe → gris générique pour la moitié du programme du Golfe</t>
         </is>
       </c>
-      <c r="E51" s="9" t="n">
+      <c r="E52" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="F52" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G51" s="9" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>tunisia.js</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>Référentiel école : postes, docs, demandes</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>1 test délégation</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>« (DT) » en dur dans 3 libellés ; articles du code du travail TUNISIEN cités au BH ; hr/accountant ne peuvent déposer aucune demande</t>
         </is>
       </c>
-      <c r="E52" s="8" t="n">
+      <c r="E53" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F52" s="8" t="inlineStr">
+      <c r="F53" s="8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G52" s="8" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>workbench.js</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>« Ce qui attend MA décision »</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>4 tests (bien couvert)</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>hr/accountant/enseignant… SANS file (la RH ne voit pas la paie en attente !) ; deref chain sans garde peut blanchir le tableau de bord</t>
         </is>
       </c>
-      <c r="E53" s="7" t="n">
+      <c r="E54" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>OUVERT</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>remote.js (app)</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>La couture client↔serveur</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="inlineStr">
-        <is>
-          <t>AUCUN TEST</t>
-        </is>
-      </c>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>pushing bloqué à jamais à la 1re coupure (corrigé) ; 409 = écrasement local (copie de sauvegarde ajoutée) ; blob entier à chaque push ; jeton en localStorage</t>
-        </is>
-      </c>
-      <c r="E54" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G54" s="8" t="inlineStr">
-        <is>
-          <t>CORRIGÉ 2026-07-25 (6dcc445) (try/finally + copie)</t>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>OUVERT</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>RemoteGate.jsx (app)</t>
+          <t>remote.js (app)</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>Porte du mode serveur</t>
+          <t>La couture client↔serveur</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>AUCUN</t>
+          <t>AUCUN TEST</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>2e écran de connexion non brandé FR-seulement ; PAS de « mot de passe oublié » (le vrai mode client !) ; jeton expiré = boucle de rechargement</t>
+          <t>pushing bloqué à jamais à la 1re coupure (corrigé) ; 409 = écrasement local (copie de sauvegarde ajoutée) ; blob entier à chaque push ; jeton en localStorage</t>
         </is>
       </c>
       <c r="E55" s="8" t="n">
@@ -4089,6 +4089,41 @@
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>CORRIGÉ 2026-07-25 (6dcc445) (try/finally + copie)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>RemoteGate.jsx (app)</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Porte du mode serveur</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>AUCUN</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>2e écran de connexion non brandé FR-seulement ; PAS de « mot de passe oublié » (le vrai mode client !) ; jeton expiré = boucle de rechargement</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>OUVERT</t>
         </is>
